--- a/reports/一级子公司A_利润表_2025-10.xlsx
+++ b/reports/一级子公司A_利润表_2025-10.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>180387663</v>
+        <v>183337408</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>175798849</v>
+        <v>174704515</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1694576033</v>
+        <v>1694215212</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>713987</v>
+        <v>715429</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>6910923</v>
+        <v>6906303</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>616957</v>
+        <v>621864</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>5994344</v>
+        <v>5994813</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>524405</v>
+        <v>527612</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5078577</v>
+        <v>5082467</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>480109</v>
+        <v>485556</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>4671069</v>
+        <v>4677430</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>262255</v>
+        <v>263724</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2538262</v>
+        <v>2542588</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>209077</v>
+        <v>210676</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2030577</v>
+        <v>2034100</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>177580873</v>
+        <v>180512547</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>172992059</v>
+        <v>171879654</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>88988537</v>
+        <v>88586665</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>858336517</v>
+        <v>858971760</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1634496</v>
+        <v>1620749</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>15751511</v>
+        <v>15746023</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1472578</v>
+        <v>1462261</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>14229681</v>
+        <v>14213834</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>79155043</v>
+        <v>78456551</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>762050621</v>
+        <v>761119403</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1674584</v>
+        <v>1675921</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>16260675</v>
+        <v>16239602</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>738369</v>
+        <v>734126</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>7115391</v>
+        <v>7105870</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2613906</v>
+        <v>2631122</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>25404664</v>
+        <v>25391620</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1155832</v>
+        <v>1157869</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>11178484</v>
+        <v>11173123</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4499073</v>
+        <v>4533307</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>43687184</v>
+        <v>43694145</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89741</v>
+        <v>90460</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>899646</v>
+        <v>900627</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2406338</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>23185661</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1602788</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>15459231</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>120254694</v>
+        <v>128397410</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>107566355</v>
+        <v>107015558</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>105362341</v>
+        <v>104818076</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1015669592</v>
+        <v>1016417275</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2204014</v>
+        <v>2197482</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>21334206</v>
+        <v>21336843</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3970618</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>38591046</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1270076</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>12344810</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>794212</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>7713877</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>954350</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>9256325</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>717163</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>6943268</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>479165</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>4630252</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>400130</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3860112</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1838594</v>
+        <v>1845661</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>17778892</v>
+        <v>17784841</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1409336</v>
+        <v>1424882</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>13711787</v>
+        <v>13725025</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1153844</v>
+        <v>1160909</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>11169978</v>
+        <v>11186275</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8676616</v>
+        <v>8751002</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>84275975</v>
+        <v>84415902</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349578</v>
+        <v>368447</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3497459</v>
+        <v>3559530</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>669707</v>
+        <v>670119</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>6696729</v>
+        <v>6704928</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>759765</v>
+        <v>670119</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>7597693</v>
+        <v>6704928</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90343</v>
+        <v>89668</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>900010</v>
+        <v>899893</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>340302</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3417929</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>694584</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>6750818</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>226948</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2277441</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>170459</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1708117</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>284670</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2847477</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>998551</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>9646834</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>152468</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1519923</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114520</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1140477</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>190995</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1901550</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>133665</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1331424</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>95368</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>951078</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>76157</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>760759</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>56995</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>570395</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>57326179</v>
+        <v>54530728</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>66310123</v>
+        <v>61150568</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>396983</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3858705</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>94505</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>949066</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>150648</v>
+        <v>149327</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1501032</v>
+        <v>1498302</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>57175531</v>
+        <v>54778384</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5319074</v>
+        <v>5295355</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>53030577</v>
+        <v>52955231</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>51856457</v>
+        <v>49483029</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>51856457</v>
+        <v>49483029</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>51856457</v>
+        <v>49483029</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>51856457</v>
+        <v>49483029</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>51856457</v>
+        <v>49483029</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
